--- a/templates/grades_import_template.xlsx
+++ b/templates/grades_import_template.xlsx
@@ -1294,10 +1294,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A50:F50"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/grades_import_template.xlsx
+++ b/templates/grades_import_template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成绩导入模板" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="成绩导入模板" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2552,8 +2552,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A122:F122"/>
     <mergeCell ref="A121:F121"/>
-    <mergeCell ref="A122:F122"/>
     <mergeCell ref="A123:F123"/>
     <mergeCell ref="A124:F124"/>
   </mergeCells>

--- a/templates/grades_import_template.xlsx
+++ b/templates/grades_import_template.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>王怀铮</t>
+          <t>蔡煜安</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>李亦辰</t>
+          <t>陈泽勋</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>陈楷烨</t>
+          <t>陈梓轩</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>涂思铭</t>
+          <t>洪健城</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>黄罄易</t>
+          <t>黄镓艺</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>吴建霖</t>
+          <t>江臻胤</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1884,12 +1884,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>黄启亮</t>
+          <t>练长鑫</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>张煜林</t>
+          <t>廖柏辰</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>黄贵权</t>
+          <t>林梓琦</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>夏逢瑞</t>
+          <t>苏俊敏</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>苏学彬</t>
+          <t>张煜锋</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>胡梓灿</t>
+          <t>陈煌仪</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>黄铄淞</t>
+          <t>王璟逸</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>何礼轩</t>
+          <t>张瀚琪</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>黄辰隽</t>
+          <t>林禹衡</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2037,12 +2037,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>肖锐骐</t>
+          <t>王茁恺</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>康高钥</t>
+          <t>黄蓥芯</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>庄程珺</t>
+          <t>杨子妍</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>魏瀚彬</t>
+          <t>曾雅琳</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>陈芷嫣</t>
+          <t>苏恩怡</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2122,12 +2122,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>兰勇炘</t>
+          <t>王希恩</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>吴世垚</t>
+          <t>姚庄诚</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>庄文焘</t>
+          <t>张宇彤</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>林昕妤</t>
+          <t>李嘉勋</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>姚翔方</t>
+          <t>林凯楠</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>黄永帅</t>
+          <t>陈玥颖</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>林煌宸</t>
+          <t>费奕文</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>傅铂诗</t>
+          <t>梁世弘</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>黄佳烨</t>
+          <t>吕紫翔</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2275,12 +2275,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>许雯淇</t>
+          <t>李秋华</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>赖瀚宸</t>
+          <t>许宏伟</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>徐子嘉</t>
+          <t>陈文铄</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>郭宇珊</t>
+          <t>赵梓言</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>赵娅慧</t>
+          <t>苏瑾萱</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>谢优优</t>
+          <t>陈嘉俊</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
@@ -2377,24 +2377,24 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>赖雨涵</t>
+          <t>郑沛文</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>六年级3班</t>
+          <t>五年级6班</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>王雅昕</t>
+          <t>王怀铮</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2406,12 +2406,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>林熙妍</t>
+          <t>李亦辰</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2423,12 +2423,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>林若冰</t>
+          <t>陈楷烨</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2440,12 +2440,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>朱雅晨</t>
+          <t>涂思铭</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>张杨唯一</t>
+          <t>黄罄易</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2474,12 +2474,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>许文强</t>
+          <t>吴建霖</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>林彦君</t>
+          <t>黄启亮</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2508,15 +2508,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>罗少卿</t>
+          <t>张煜林</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>黄贵权</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
         <is>
           <t>六年级3班</t>
         </is>
@@ -2525,37 +2542,632 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>说明事项：</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>夏逢瑞</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1. 成绩可填写：优、良、及格、待及格，请勿使用其他评分方式</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>苏学彬</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2. 请勿修改学号、姓名和班级</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>胡梓灿</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>黄铄淞</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>何礼轩</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>黄辰隽</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>肖锐骐</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>康高钥</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>庄程珺</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>魏瀚彬</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>陈芷嫣</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>兰勇炘</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>吴世垚</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>庄文焘</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>林昕妤</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>姚翔方</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>黄永帅</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>林煌宸</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>傅铂诗</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>黄佳烨</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>许雯淇</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>赖瀚宸</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>徐子嘉</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>郭宇珊</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>赵娅慧</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>谢优优</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>赖雨涵</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>王雅昕</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>林熙妍</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>林若冰</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>朱雅晨</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>张杨唯一</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>许文强</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>林彦君</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>罗少卿</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>六年级3班</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>说明事项：</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1. 成绩可填写：优、良、及格、待及格，请勿使用其他评分方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2. 请勿修改学号、姓名和班级</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
           <t>3. 导入时只需填写有变更的成绩</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A121:F121"/>
-    <mergeCell ref="A122:F122"/>
-    <mergeCell ref="A123:F123"/>
-    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A157:F157"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A160:F160"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
